--- a/CHESS_low_crested_breakwater_inputs.xlsx
+++ b/CHESS_low_crested_breakwater_inputs.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\StormSim_Library\PSE_Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\CHESS-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DE5E2F-D3B9-4B61-9E1D-A04795045D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA01515-445E-46B5-ABCF-100BB6509248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="11670" windowWidth="28800" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="4635" windowWidth="28800" windowHeight="15270"/>
   </bookViews>
   <sheets>
     <sheet name="lowcrestedbw" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -456,13 +456,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -474,30 +474,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -654,115 +654,117 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1081,17 +1083,17 @@
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="101.7109375" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="153.42578125" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" customWidth="1"/>
-    <col min="7" max="7" width="84.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="101.7109375" customWidth="true"/>
+    <col min="2" max="2" width="53.5703125" customWidth="true"/>
+    <col min="3" max="3" width="19.28515625" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="63" customWidth="true"/>
+    <col min="6" max="6" width="28.42578125" customWidth="true"/>
+    <col min="7" max="7" width="84.28515625" bestFit="true" customWidth="true"/>
+    <col min="8" max="8" width="46.140625" customWidth="true"/>
+    <col min="9" max="9" width="13.5703125" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
@@ -1135,7 +1137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>8</v>
       </c>
@@ -1161,7 +1163,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -1187,7 +1189,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -1205,7 +1207,7 @@
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
     </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
@@ -1225,7 +1227,7 @@
       <c r="H6" s="36"/>
       <c r="I6" s="36"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
@@ -1251,7 +1253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>30</v>
       </c>
@@ -1277,7 +1279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
@@ -1303,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
@@ -1317,7 +1319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
@@ -1331,7 +1333,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>44</v>
       </c>
@@ -1342,10 +1344,10 @@
         <v>46</v>
       </c>
       <c r="D12" s="2">
-        <v>176.45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="true" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
@@ -1359,7 +1361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>49</v>
       </c>
@@ -1373,7 +1375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>51</v>
       </c>
@@ -1387,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>53</v>
       </c>
@@ -1401,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>55</v>
       </c>
@@ -1415,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>57</v>
       </c>
@@ -1429,7 +1431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>59</v>
       </c>
@@ -1443,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
         <v>61</v>
       </c>
@@ -1457,13 +1459,13 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="true" x14ac:dyDescent="0.25">
       <c r="A21" s="41"/>
       <c r="B21" s="40"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
         <v>64</v>
       </c>
@@ -1471,7 +1473,7 @@
       <c r="C22" s="33"/>
       <c r="D22" s="33"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="true" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>65</v>
       </c>
@@ -1499,7 +1501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>68</v>
       </c>
@@ -1513,7 +1515,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>71</v>
       </c>
@@ -1527,7 +1529,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>74</v>
       </c>
@@ -1541,13 +1543,13 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" x14ac:dyDescent="0.25">
       <c r="A28" s="33"/>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>76</v>
       </c>
@@ -1555,7 +1557,7 @@
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>3</v>
       </c>
@@ -1569,7 +1571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="true" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
         <v>77</v>
       </c>
@@ -1583,7 +1585,7 @@
         <v>180.1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="true" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>79</v>
       </c>
@@ -1597,7 +1599,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>81</v>
       </c>
@@ -1611,7 +1613,7 @@
         <v>176.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>83</v>
       </c>
@@ -1625,7 +1627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>85</v>
       </c>
@@ -1639,7 +1641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>116</v>
       </c>
@@ -1653,7 +1655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="15.75" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A37" s="31" t="s">
         <v>118</v>
       </c>
@@ -1667,13 +1669,13 @@
         <v>173.99</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
     </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>87</v>
       </c>
@@ -1681,7 +1683,7 @@
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
     </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>3</v>
       </c>
@@ -1695,7 +1697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>88</v>
       </c>
@@ -1709,7 +1711,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>90</v>
       </c>
@@ -1723,7 +1725,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>93</v>
       </c>
@@ -1737,7 +1739,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>96</v>
       </c>
@@ -1751,7 +1753,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" ht="60.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
         <v>99</v>
       </c>
@@ -1765,13 +1767,13 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
     </row>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>101</v>
       </c>
@@ -1779,7 +1781,7 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
     </row>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" ht="15.75" customHeight="true" thickBot="true" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>3</v>
       </c>
@@ -1793,7 +1795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>102</v>
       </c>
@@ -1807,7 +1809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>104</v>
       </c>
@@ -1821,7 +1823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>106</v>
       </c>
@@ -1835,7 +1837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>108</v>
       </c>
@@ -1849,7 +1851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>110</v>
       </c>
@@ -1863,7 +1865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="true" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>112</v>
       </c>
@@ -1877,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>114</v>
       </c>
@@ -1891,13 +1893,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
     </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="19.5" customHeight="true" x14ac:dyDescent="0.25"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="D36" name="Range1_1_3_1_8"/>
